--- a/db/bankstatements/2026-2027/corpus-account/unmatched_transactions.xlsx
+++ b/db/bankstatements/2026-2027/corpus-account/unmatched_transactions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Unmatched Transactions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -177,15 +177,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -559,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -583,7 +574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated on 13-Oct-2026 08:13 AM | Source: sep1-oct13-2026.xls | Total Unmatched: 2 | Total Amount: Rs. 13,000.00</t>
+          <t>Generated on 16-Oct-2026 07:57 PM | Source: sep1-oct16-2026.xls | Total Unmatched: 1 | Total Amount: Rs. 6,500.00</t>
         </is>
       </c>
     </row>
@@ -648,12 +639,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1 Oct 2026</t>
+          <t>10 Oct 2026</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1 Oct 2026</t>
+          <t>10 Oct 2026</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -666,75 +657,40 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>TRANSFER FROM 4897735162098 /</t>
+          <t>TRANSFER FROM 4897737162096 /</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>BY TRANSFER-UPI/CR/664013712275/NIKHIL K/HDFC/8005524064/F01 W--</t>
+          <t>BY TRANSFER-UPI/CR/628362488200/PRASHANT/ICIC/fossil.rvc/Prash--</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>10 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>10 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>TRANSFER FROM 4897737162096 /</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>BY TRANSFER-UPI/CR/628362488200/PRASHANT/ICIC/fossil.rvc/Prash--</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>TOTAL UNMATCHED</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15">
-        <f>SUM(D6:D7)</f>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="12">
+        <f>SUM(D6:D6)</f>
         <v/>
       </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
